--- a/ScriptedWorkflow/Dev-Drive/Dev-Drive/RepositoryList.xlsx
+++ b/ScriptedWorkflow/Dev-Drive/Dev-Drive/RepositoryList.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kernm.devcontainer.envsetup\Dev-Drive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VHDXToFolders\ScriptedWorkflow\Dev-Drive\Dev-Drive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B54545-7646-4DCA-B8DF-B1154A17446E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5605C8B5-D707-41F7-9CFD-4562BE220D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="255" windowWidth="23040" windowHeight="13425" xr2:uid="{1CAB5FCE-5169-4CBB-A297-E7E738FC7A53}"/>
+    <workbookView xWindow="19425" yWindow="375" windowWidth="38370" windowHeight="20505" xr2:uid="{1CAB5FCE-5169-4CBB-A297-E7E738FC7A53}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Repo Map" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
   <si>
     <t>Run Id</t>
   </si>
@@ -81,6 +81,108 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>CheckImages</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/CheckImages/CheckImages</t>
+  </si>
+  <si>
+    <t>CustomerSolutions</t>
+  </si>
+  <si>
+    <t>CustomerAccountServiceV2</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/CustomerSolutions/CustomerAccountServiceV2</t>
+  </si>
+  <si>
+    <t>EnterpriseUserAuthentication</t>
+  </si>
+  <si>
+    <t>CustomerIdentityProvider</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/EnterpriseUserAuthentication/CustomerIdentityProvider</t>
+  </si>
+  <si>
+    <t>EuasV4</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/EnterpriseUserAuthentication/EuasV4</t>
+  </si>
+  <si>
+    <t>LoanMonitoring</t>
+  </si>
+  <si>
+    <t>LoanMonitoringAPI</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/LoanMonitoring/LoanMonitoringAPI</t>
+  </si>
+  <si>
+    <t>MyAccount</t>
+  </si>
+  <si>
+    <t>MyAccount.Hub</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/MyAccount/MyAccount.Hub</t>
+  </si>
+  <si>
+    <t>MyAccount.MyFinancials</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/MyAccount/MyAccount.MyFinancials</t>
+  </si>
+  <si>
+    <t>MyAccountAdmin</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/MyAccount/MyAccountAdmin</t>
+  </si>
+  <si>
+    <t>OperationScope</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/OperationScope/OperationScope</t>
+  </si>
+  <si>
+    <t>QuoteCalculator</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/QuoteCalculator/QuoteCalculator</t>
+  </si>
+  <si>
+    <t>SecureImageCapture</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/SecureImageCapture/SecureImageCapture</t>
+  </si>
+  <si>
+    <t>Solutions Delivery</t>
+  </si>
+  <si>
+    <t>UniversalMobilePlatform_XP_API</t>
+  </si>
+  <si>
+    <t>git@ssh.dev.azure.com:v3/fcsamerica/Solutions%20Delivery/UniversalMobilePlatform_XP_API</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>AppDev-DS</t>
+  </si>
+  <si>
+    <t>ProjectId (WorkItem)</t>
+  </si>
+  <si>
+    <t>Pull Templates</t>
   </si>
 </sst>
 </file>
@@ -136,16 +238,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C2CBA0A3-D279-4FD3-8122-216B24F324C9}" name="Table1" displayName="Table1" ref="A1:G3" totalsRowShown="0">
-  <autoFilter ref="A1:G3" xr:uid="{C2CBA0A3-D279-4FD3-8122-216B24F324C9}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C2CBA0A3-D279-4FD3-8122-216B24F324C9}" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <autoFilter ref="A1:J15" xr:uid="{C2CBA0A3-D279-4FD3-8122-216B24F324C9}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F49F807F-B7C3-430C-BA3D-07FC39D9D5AB}" name="Run Id"/>
     <tableColumn id="2" xr3:uid="{FBC46471-5ECA-4285-ADDD-F3E54DF13576}" name="Index ID"/>
+    <tableColumn id="8" xr3:uid="{761B0DE2-98BE-44F3-861B-0E6D31459C07}" name="Team Name"/>
     <tableColumn id="3" xr3:uid="{DC8EDDD4-3102-4163-8B68-A1EBE7579AA4}" name="Project Group (Team) Name"/>
     <tableColumn id="4" xr3:uid="{FD74E632-4CA2-457C-A6BC-3DCCC2DB94E3}" name="Project Name"/>
+    <tableColumn id="6" xr3:uid="{DE43F4B2-DE13-49CB-8782-64E0C77FCD04}" name="Repos"/>
+    <tableColumn id="9" xr3:uid="{53ACF071-BADC-4F70-946C-5FDA29E55BEA}" name="ProjectId (WorkItem)"/>
     <tableColumn id="5" xr3:uid="{A9EA8A29-445C-4052-B003-D19130E4614A}" name="Drive Letter"/>
     <tableColumn id="7" xr3:uid="{35B4E51E-B38B-4951-AC83-08C6E0563898}" name="Create Script"/>
-    <tableColumn id="6" xr3:uid="{DE43F4B2-DE13-49CB-8782-64E0C77FCD04}" name="Repos"/>
+    <tableColumn id="10" xr3:uid="{7FEEF592-4D8C-483D-A3FA-CDDD500470FD}" name="Pull Templates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -468,16 +573,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E01E1C-8BAA-44E0-96CD-57033B705BE5}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="6" width="13.85546875" customWidth="1"/>
+    <col min="2" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="103.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="103.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -485,71 +594,471 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>284126</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>284126</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>284126</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>284126</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>284126</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>284126</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10">
+        <v>284126</v>
+      </c>
+      <c r="H10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11">
+        <v>284126</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12">
+        <v>284126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13">
+        <v>284126</v>
+      </c>
+      <c r="H13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14">
+        <v>284126</v>
+      </c>
+      <c r="H14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15">
+        <v>284126</v>
+      </c>
+      <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>